--- a/result/sensitivity_performance.xlsx
+++ b/result/sensitivity_performance.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjyan\Desktop\ppt\ppt-2026年\文章素材\文章正文\scGEM_benchmark\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjyan\Documents\GitHub\scGEM_benchmark_NCS\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09437A-7423-4E65-914A-D75DEB4B523C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{773B09EA-B6C6-4101-B3C5-8BC826EA7FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34515" yWindow="615" windowWidth="17550" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12030" yWindow="1710" windowWidth="23010" windowHeight="16515" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -168,7 +181,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -293,6 +306,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -345,9 +378,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -393,9 +423,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
@@ -422,6 +449,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -713,93 +746,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:64" x14ac:dyDescent="0.25">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="40" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="36" t="s">
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="36"/>
-      <c r="U1" s="36"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="40" t="s">
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="X1" s="36"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="36" t="s">
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="AE1" s="36"/>
-      <c r="AF1" s="36"/>
-      <c r="AG1" s="36"/>
-      <c r="AH1" s="36"/>
-      <c r="AI1" s="36"/>
-      <c r="AJ1" s="36"/>
-      <c r="AK1" s="40" t="s">
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="AL1" s="36"/>
-      <c r="AM1" s="36"/>
-      <c r="AN1" s="36"/>
-      <c r="AO1" s="36"/>
-      <c r="AP1" s="36"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="36" t="s">
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="35"/>
+      <c r="AR1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AS1" s="36"/>
-      <c r="AT1" s="36"/>
-      <c r="AU1" s="36"/>
-      <c r="AV1" s="36"/>
-      <c r="AW1" s="36"/>
-      <c r="AX1" s="36"/>
-      <c r="AY1" s="40" t="s">
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="AZ1" s="36"/>
-      <c r="BA1" s="36"/>
-      <c r="BB1" s="36"/>
-      <c r="BC1" s="36"/>
-      <c r="BD1" s="36"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="36" t="s">
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+      <c r="BB1" s="34"/>
+      <c r="BC1" s="34"/>
+      <c r="BD1" s="34"/>
+      <c r="BE1" s="35"/>
+      <c r="BF1" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="BG1" s="36"/>
-      <c r="BH1" s="36"/>
-      <c r="BI1" s="36"/>
-      <c r="BJ1" s="36"/>
-      <c r="BK1" s="36"/>
-      <c r="BL1" s="37"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
+      <c r="BJ1" s="34"/>
+      <c r="BK1" s="34"/>
+      <c r="BL1" s="35"/>
     </row>
     <row r="2" spans="1:64" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39"/>
+      <c r="A2" s="37"/>
       <c r="B2" s="1">
         <v>1</v>
       </c>
@@ -1120,67 +1153,67 @@
       <c r="AQ3" s="12">
         <v>75.5</v>
       </c>
-      <c r="AR3" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS3" s="16">
-        <v>0.67353535353535399</v>
-      </c>
-      <c r="AT3" s="16">
-        <v>0.567676767676768</v>
-      </c>
-      <c r="AU3" s="16">
-        <v>0.53454545454545499</v>
-      </c>
-      <c r="AV3" s="16">
-        <v>0.55636363636363595</v>
-      </c>
-      <c r="AW3" s="16">
-        <v>0.50060606060606105</v>
-      </c>
-      <c r="AX3" s="16">
-        <v>0.53616161616161595</v>
-      </c>
-      <c r="AY3" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ3" s="16">
+      <c r="AR3" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="39">
+        <v>0.29986848464659338</v>
+      </c>
+      <c r="AT3" s="39">
+        <v>5.0331447144978753E-2</v>
+      </c>
+      <c r="AU3" s="39">
+        <v>9.9066630760503774E-3</v>
+      </c>
+      <c r="AV3" s="39">
+        <v>6.1129784627639329E-3</v>
+      </c>
+      <c r="AW3" s="39">
+        <v>-5.6502282692220867E-3</v>
+      </c>
+      <c r="AX3" s="40">
+        <v>2.550917428596762E-2</v>
+      </c>
+      <c r="AY3" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="15">
         <v>0.40889264528311398</v>
       </c>
-      <c r="BA3" s="16">
+      <c r="BA3" s="15">
         <v>8.5403111781019905E-2</v>
       </c>
-      <c r="BB3" s="16">
+      <c r="BB3" s="15">
         <v>5.40540189231331E-2</v>
       </c>
-      <c r="BC3" s="16">
+      <c r="BC3" s="15">
         <v>2.5305088101332002E-2</v>
       </c>
-      <c r="BD3" s="16">
+      <c r="BD3" s="15">
         <v>1.04112719875523E-2</v>
       </c>
-      <c r="BE3" s="18">
+      <c r="BE3" s="17">
         <v>4.6090461374961499E-2</v>
       </c>
-      <c r="BF3" s="19">
+      <c r="BF3" s="18">
         <v>0.28218471861130701</v>
       </c>
-      <c r="BG3" s="16">
+      <c r="BG3" s="15">
         <v>0.28510000000000002</v>
       </c>
-      <c r="BH3" s="16">
+      <c r="BH3" s="15">
         <v>0.28633490927099597</v>
       </c>
-      <c r="BI3" s="16">
+      <c r="BI3" s="15">
         <v>0.28006968584333403</v>
       </c>
-      <c r="BJ3" s="16">
+      <c r="BJ3" s="15">
         <v>0.27355688923662103</v>
       </c>
-      <c r="BK3" s="16">
+      <c r="BK3" s="15">
         <v>0.2707</v>
       </c>
-      <c r="BL3" s="18">
+      <c r="BL3" s="17">
         <v>0.26500000000000001</v>
       </c>
     </row>
@@ -1314,67 +1347,67 @@
       <c r="AQ4" s="12">
         <v>48.5</v>
       </c>
-      <c r="AR4" s="15">
-        <v>0.98750000000000004</v>
-      </c>
-      <c r="AS4" s="16">
-        <v>0.80080808080808097</v>
-      </c>
-      <c r="AT4" s="16">
-        <v>0.56282828282828301</v>
-      </c>
-      <c r="AU4" s="16">
-        <v>0.57878787878787896</v>
-      </c>
-      <c r="AV4" s="16">
-        <v>0.56808080808080796</v>
-      </c>
-      <c r="AW4" s="16">
-        <v>0.54626262626262601</v>
-      </c>
-      <c r="AX4" s="16">
-        <v>0.52282828282828298</v>
-      </c>
-      <c r="AY4" s="17">
+      <c r="AR4" s="16">
+        <v>0.97175810360220838</v>
+      </c>
+      <c r="AS4" s="15">
+        <v>0.55564858081948132</v>
+      </c>
+      <c r="AT4" s="15">
+        <v>5.914316134854216E-2</v>
+      </c>
+      <c r="AU4" s="15">
+        <v>5.7646995016300953E-2</v>
+      </c>
+      <c r="AV4" s="15">
+        <v>2.2500472442864912E-2</v>
+      </c>
+      <c r="AW4" s="15">
+        <v>8.9560560139025915E-4</v>
+      </c>
+      <c r="AX4" s="17">
+        <v>-5.3858945181923298E-3</v>
+      </c>
+      <c r="AY4" s="16">
         <v>0.95926742202225901</v>
       </c>
-      <c r="AZ4" s="16">
+      <c r="AZ4" s="15">
         <v>0.614853420089709</v>
       </c>
-      <c r="BA4" s="16">
+      <c r="BA4" s="15">
         <v>0.15906913086959401</v>
       </c>
-      <c r="BB4" s="16">
+      <c r="BB4" s="15">
         <v>0.116600190745149</v>
       </c>
-      <c r="BC4" s="16">
+      <c r="BC4" s="15">
         <v>3.62038230106815E-2</v>
       </c>
-      <c r="BD4" s="16">
+      <c r="BD4" s="15">
         <v>2.0571056492977899E-2</v>
       </c>
-      <c r="BE4" s="18">
+      <c r="BE4" s="17">
         <v>1.08458415153231E-2</v>
       </c>
-      <c r="BF4" s="19">
+      <c r="BF4" s="18">
         <v>0.2731698102042609</v>
       </c>
-      <c r="BG4" s="16">
+      <c r="BG4" s="15">
         <v>0.27085327568388701</v>
       </c>
-      <c r="BH4" s="16">
+      <c r="BH4" s="15">
         <v>0.26268363198116002</v>
       </c>
-      <c r="BI4" s="16">
+      <c r="BI4" s="15">
         <v>0.254369039627107</v>
       </c>
-      <c r="BJ4" s="16">
+      <c r="BJ4" s="15">
         <v>0.249442331509314</v>
       </c>
-      <c r="BK4" s="16">
+      <c r="BK4" s="15">
         <v>0.248433930106815</v>
       </c>
-      <c r="BL4" s="18">
+      <c r="BL4" s="17">
         <v>0.24399999999999999</v>
       </c>
     </row>
@@ -1508,67 +1541,67 @@
       <c r="AQ5" s="12">
         <v>23.5</v>
       </c>
-      <c r="AR5" s="15">
-        <v>0.89290000000000003</v>
-      </c>
-      <c r="AS5" s="16">
-        <v>0.95232323232323202</v>
-      </c>
-      <c r="AT5" s="16">
-        <v>0.66222222222222205</v>
-      </c>
-      <c r="AU5" s="16">
-        <v>0.566464646464646</v>
-      </c>
-      <c r="AV5" s="16">
-        <v>0.56323232323232297</v>
-      </c>
-      <c r="AW5" s="16">
-        <v>0.530909090909091</v>
-      </c>
-      <c r="AX5" s="16">
-        <v>0.547474747474747</v>
-      </c>
-      <c r="AY5" s="17">
+      <c r="AR5" s="16">
+        <v>0.75939179087161712</v>
+      </c>
+      <c r="AS5" s="15">
+        <v>0.8921667577123108</v>
+      </c>
+      <c r="AT5" s="15">
+        <v>0.273480092157177</v>
+      </c>
+      <c r="AU5" s="15">
+        <v>6.5596897514644523E-2</v>
+      </c>
+      <c r="AV5" s="15">
+        <v>8.6051505774531162E-2</v>
+      </c>
+      <c r="AW5" s="15">
+        <v>-1.6718594011197619E-2</v>
+      </c>
+      <c r="AX5" s="17">
+        <v>-3.3704487494699694E-3</v>
+      </c>
+      <c r="AY5" s="16">
         <v>0.80293936916360997</v>
       </c>
-      <c r="AZ5" s="16">
+      <c r="AZ5" s="15">
         <v>0.88801378420865995</v>
       </c>
-      <c r="BA5" s="16">
+      <c r="BA5" s="15">
         <v>0.29206267029039001</v>
       </c>
-      <c r="BB5" s="16">
+      <c r="BB5" s="15">
         <v>7.2019124034270604E-2</v>
       </c>
-      <c r="BC5" s="16">
+      <c r="BC5" s="15">
         <v>8.9220652077036097E-2</v>
       </c>
-      <c r="BD5" s="16">
+      <c r="BD5" s="15">
         <v>2.7304190237248901E-3</v>
       </c>
-      <c r="BE5" s="18">
+      <c r="BE5" s="17">
         <v>2.0748007666843801E-2</v>
       </c>
-      <c r="BF5" s="19">
+      <c r="BF5" s="18">
         <v>0.26489993522451599</v>
       </c>
-      <c r="BG5" s="16">
+      <c r="BG5" s="15">
         <v>0.25064930507369099</v>
       </c>
-      <c r="BH5" s="16">
+      <c r="BH5" s="15">
         <v>0.243818951785786</v>
       </c>
-      <c r="BI5" s="16">
+      <c r="BI5" s="15">
         <v>0.24178162792897201</v>
       </c>
-      <c r="BJ5" s="16">
+      <c r="BJ5" s="15">
         <v>0.23640306963816499</v>
       </c>
-      <c r="BK5" s="16">
+      <c r="BK5" s="15">
         <v>0.236169258740239</v>
       </c>
-      <c r="BL5" s="18">
+      <c r="BL5" s="17">
         <v>0.23250000000000001</v>
       </c>
     </row>
@@ -1702,67 +1735,67 @@
       <c r="AQ6" s="12">
         <v>11.1111</v>
       </c>
-      <c r="AR6" s="15">
-        <v>0.84809999999999997</v>
-      </c>
-      <c r="AS6" s="16">
-        <v>0.83232323232323202</v>
-      </c>
-      <c r="AT6" s="16">
-        <v>0.57939393939393902</v>
-      </c>
-      <c r="AU6" s="16">
-        <v>0.44747474747474703</v>
-      </c>
-      <c r="AV6" s="16">
-        <v>0.44568130282416002</v>
-      </c>
-      <c r="AW6" s="16">
-        <v>0.50023375409069704</v>
-      </c>
-      <c r="AX6" s="16">
-        <v>0.449804164089878</v>
-      </c>
-      <c r="AY6" s="17">
+      <c r="AR6" s="16">
+        <v>0.67543117587141555</v>
+      </c>
+      <c r="AS6" s="15">
+        <v>0.63860457825589689</v>
+      </c>
+      <c r="AT6" s="15">
+        <v>0.13663615235897658</v>
+      </c>
+      <c r="AU6" s="15">
+        <v>2.619163002377663E-3</v>
+      </c>
+      <c r="AV6" s="15">
+        <v>-4.5282686422595444E-3</v>
+      </c>
+      <c r="AW6" s="15">
+        <v>-1.6989022826525434E-2</v>
+      </c>
+      <c r="AX6" s="17">
+        <v>-1.4599783669177965E-2</v>
+      </c>
+      <c r="AY6" s="16">
         <v>0.75428590150538799</v>
       </c>
-      <c r="AZ6" s="16">
+      <c r="AZ6" s="15">
         <v>0.68931667804805197</v>
       </c>
-      <c r="BA6" s="16">
+      <c r="BA6" s="15">
         <v>0.17345389633738401</v>
       </c>
-      <c r="BB6" s="16">
+      <c r="BB6" s="15">
         <v>1.6746915357801598E-2</v>
       </c>
-      <c r="BC6" s="16">
+      <c r="BC6" s="15">
         <v>4.24212160092345E-2</v>
       </c>
-      <c r="BD6" s="16">
+      <c r="BD6" s="15">
         <v>6.9285249909376602E-3</v>
       </c>
-      <c r="BE6" s="18">
+      <c r="BE6" s="17">
         <v>1.02099500495805E-2</v>
       </c>
-      <c r="BF6" s="19">
+      <c r="BF6" s="18">
         <v>0.25821549023574486</v>
       </c>
-      <c r="BG6" s="16">
+      <c r="BG6" s="15">
         <v>0.241912678653526</v>
       </c>
-      <c r="BH6" s="16">
+      <c r="BH6" s="15">
         <v>0.24132242505329299</v>
       </c>
-      <c r="BI6" s="16">
+      <c r="BI6" s="15">
         <v>0.23545919950914501</v>
       </c>
-      <c r="BJ6" s="16">
+      <c r="BJ6" s="15">
         <v>0.232459787328363</v>
       </c>
-      <c r="BK6" s="16">
+      <c r="BK6" s="15">
         <v>0.228095005916746</v>
       </c>
-      <c r="BL6" s="18">
+      <c r="BL6" s="17">
         <v>0.227018654146913</v>
       </c>
     </row>
@@ -1896,67 +1929,67 @@
       <c r="AQ7" s="12">
         <v>87.5</v>
       </c>
-      <c r="AR7" s="15">
-        <v>0.94140000000000001</v>
-      </c>
-      <c r="AS7" s="16">
-        <v>0.74020202020201997</v>
-      </c>
-      <c r="AT7" s="16">
-        <v>0.57858585858585898</v>
-      </c>
-      <c r="AU7" s="16">
-        <v>0.54646464646464599</v>
-      </c>
-      <c r="AV7" s="16">
-        <v>0.55800000000000005</v>
-      </c>
-      <c r="AW7" s="16">
-        <v>0.55676767676767702</v>
-      </c>
-      <c r="AX7" s="16">
-        <v>0.55232323232323199</v>
-      </c>
-      <c r="AY7" s="17">
+      <c r="AR7" s="16">
+        <v>0.86753393871845996</v>
+      </c>
+      <c r="AS7" s="39">
+        <v>0.42168284595597699</v>
+      </c>
+      <c r="AT7" s="39">
+        <v>7.7613330634399999E-2</v>
+      </c>
+      <c r="AU7" s="39">
+        <v>-1.7152396160344099E-2</v>
+      </c>
+      <c r="AV7" s="39">
+        <v>5.17116996962766E-3</v>
+      </c>
+      <c r="AW7" s="39">
+        <v>-3.4128027871561401E-3</v>
+      </c>
+      <c r="AX7" s="40">
+        <v>-3.8596046170293599E-3</v>
+      </c>
+      <c r="AY7" s="16">
         <v>0.87016895991861098</v>
       </c>
-      <c r="AZ7" s="16">
+      <c r="AZ7" s="15">
         <v>0.42438490723455102</v>
       </c>
-      <c r="BA7" s="16">
+      <c r="BA7" s="15">
         <v>0.12794424079594</v>
       </c>
-      <c r="BB7" s="16">
+      <c r="BB7" s="15">
         <v>2.8519502573453601E-3</v>
       </c>
-      <c r="BC7" s="16">
+      <c r="BC7" s="15">
         <v>2.3800000000000002E-2</v>
       </c>
-      <c r="BD7" s="16">
+      <c r="BD7" s="15">
         <v>1.48386880738348E-2</v>
       </c>
-      <c r="BE7" s="18">
+      <c r="BE7" s="17">
         <v>1.5944659835504499E-2</v>
       </c>
-      <c r="BF7" s="19">
+      <c r="BF7" s="18">
         <v>0.1343104560632134</v>
       </c>
-      <c r="BG7" s="16">
+      <c r="BG7" s="15">
         <v>0.122390735008802</v>
       </c>
-      <c r="BH7" s="16">
+      <c r="BH7" s="15">
         <v>0.121581548907725</v>
       </c>
-      <c r="BI7" s="16">
+      <c r="BI7" s="15">
         <v>0.113611766741887</v>
       </c>
-      <c r="BJ7" s="16">
+      <c r="BJ7" s="15">
         <v>0.107990304658974</v>
       </c>
-      <c r="BK7" s="16">
+      <c r="BK7" s="15">
         <v>0.105807845595298</v>
       </c>
-      <c r="BL7" s="18">
+      <c r="BL7" s="17">
         <v>0.1022</v>
       </c>
     </row>
@@ -2090,67 +2123,67 @@
       <c r="AQ8" s="12">
         <v>72.5</v>
       </c>
-      <c r="AR8" s="15">
-        <v>0.98750000000000004</v>
-      </c>
-      <c r="AS8" s="16">
-        <v>0.62787878787878804</v>
-      </c>
-      <c r="AT8" s="16">
-        <v>0.62020202020201998</v>
-      </c>
-      <c r="AU8" s="16">
-        <v>0.568888888888889</v>
-      </c>
-      <c r="AV8" s="16">
-        <v>0.56404040404040401</v>
-      </c>
-      <c r="AW8" s="16">
-        <v>0.54909090909090896</v>
-      </c>
-      <c r="AX8" s="16">
-        <v>0.53373737373737395</v>
-      </c>
-      <c r="AY8" s="17">
+      <c r="AR8" s="16">
+        <v>0.97175810360220805</v>
+      </c>
+      <c r="AS8" s="15">
+        <v>0.16760226471633799</v>
+      </c>
+      <c r="AT8" s="15">
+        <v>0.14098942584383101</v>
+      </c>
+      <c r="AU8" s="15">
+        <v>2.58337171296231E-2</v>
+      </c>
+      <c r="AV8" s="15">
+        <v>2.03160088697165E-2</v>
+      </c>
+      <c r="AW8" s="15">
+        <v>3.2292830674021502E-3</v>
+      </c>
+      <c r="AX8" s="17">
+        <v>-1.2985644981010101E-2</v>
+      </c>
+      <c r="AY8" s="16">
         <v>0.95926742202225901</v>
       </c>
-      <c r="AZ8" s="16">
+      <c r="AZ8" s="15">
         <v>0.21090015202522699</v>
       </c>
-      <c r="BA8" s="16">
+      <c r="BA8" s="15">
         <v>0.172315229283589</v>
       </c>
-      <c r="BB8" s="16">
+      <c r="BB8" s="15">
         <v>5.1206553880657799E-2</v>
       </c>
-      <c r="BC8" s="16">
+      <c r="BC8" s="15">
         <v>3.2901191880364403E-2</v>
       </c>
-      <c r="BD8" s="16">
+      <c r="BD8" s="15">
         <v>2.38839742679939E-2</v>
       </c>
-      <c r="BE8" s="18">
+      <c r="BE8" s="17">
         <v>8.4020382529803508E-3</v>
       </c>
-      <c r="BF8" s="19">
+      <c r="BF8" s="18">
         <v>9.9247694588282212E-2</v>
       </c>
-      <c r="BG8" s="16">
+      <c r="BG8" s="15">
         <v>0.10193424058429</v>
       </c>
-      <c r="BH8" s="16">
+      <c r="BH8" s="15">
         <v>0.104300493094659</v>
       </c>
-      <c r="BI8" s="16">
+      <c r="BI8" s="15">
         <v>9.7207797196848203E-2</v>
       </c>
-      <c r="BJ8" s="16">
+      <c r="BJ8" s="15">
         <v>0.1029978528806</v>
       </c>
-      <c r="BK8" s="16">
+      <c r="BK8" s="15">
         <v>0.10097295429759701</v>
       </c>
-      <c r="BL8" s="18">
+      <c r="BL8" s="17">
         <v>0.10100000000000001</v>
       </c>
     </row>
@@ -2284,67 +2317,67 @@
       <c r="AQ9" s="12">
         <v>59.5</v>
       </c>
-      <c r="AR9" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS9" s="16">
-        <v>0.97535353535353497</v>
-      </c>
-      <c r="AT9" s="16">
-        <v>0.728080808080808</v>
-      </c>
-      <c r="AU9" s="16">
-        <v>0.50666666666666704</v>
-      </c>
-      <c r="AV9" s="16">
-        <v>0.54828282828282804</v>
-      </c>
-      <c r="AW9" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="AX9" s="16">
-        <v>0.50969696969696998</v>
-      </c>
-      <c r="AY9" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ9" s="16">
+      <c r="AR9" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS9" s="15">
+        <v>0.94427289835742101</v>
+      </c>
+      <c r="AT9" s="15">
+        <v>0.418208154114806</v>
+      </c>
+      <c r="AU9" s="15">
+        <v>-1.32163464464126E-2</v>
+      </c>
+      <c r="AV9" s="15">
+        <v>-2.7925110474607399E-3</v>
+      </c>
+      <c r="AW9" s="15">
+        <v>1.06665908658877E-2</v>
+      </c>
+      <c r="AX9" s="17">
+        <v>-7.1338068302326902E-3</v>
+      </c>
+      <c r="AY9" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ9" s="15">
         <v>0.93133918008437999</v>
       </c>
-      <c r="BA9" s="16">
+      <c r="BA9" s="15">
         <v>0.443425546462897</v>
       </c>
-      <c r="BB9" s="16">
+      <c r="BB9" s="15">
         <v>4.83459714775947E-3</v>
       </c>
-      <c r="BC9" s="16">
+      <c r="BC9" s="15">
         <v>2.0850165252037301E-2</v>
       </c>
-      <c r="BD9" s="16">
+      <c r="BD9" s="15">
         <v>2.8137482245717299E-2</v>
       </c>
-      <c r="BE9" s="18">
+      <c r="BE9" s="17">
         <v>1.8881986566227301E-2</v>
       </c>
-      <c r="BF9" s="19">
+      <c r="BF9" s="18">
         <v>0.10754846194796039</v>
       </c>
-      <c r="BG9" s="16">
+      <c r="BG9" s="15">
         <v>0.106883723243703</v>
       </c>
-      <c r="BH9" s="16">
+      <c r="BH9" s="15">
         <v>0.10623515438853499</v>
       </c>
-      <c r="BI9" s="16">
+      <c r="BI9" s="15">
         <v>0.10723975385982</v>
       </c>
-      <c r="BJ9" s="16">
+      <c r="BJ9" s="15">
         <v>0.103796136870862</v>
       </c>
-      <c r="BK9" s="16">
+      <c r="BK9" s="15">
         <v>0.102792910439734</v>
       </c>
-      <c r="BL9" s="18">
+      <c r="BL9" s="17">
         <v>0.1048</v>
       </c>
     </row>
@@ -2478,67 +2511,67 @@
       <c r="AQ10" s="12">
         <v>53.5</v>
       </c>
-      <c r="AR10" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS10" s="16">
-        <v>1</v>
-      </c>
-      <c r="AT10" s="16">
-        <v>0.70828282828282796</v>
-      </c>
-      <c r="AU10" s="16">
-        <v>0.51373737373737405</v>
-      </c>
-      <c r="AV10" s="16">
-        <v>0.50424242424242405</v>
-      </c>
-      <c r="AW10" s="16">
-        <v>0.51535353535353501</v>
-      </c>
-      <c r="AX10" s="16">
-        <v>0.53010000000000002</v>
-      </c>
-      <c r="AY10" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ10" s="16">
-        <v>1</v>
-      </c>
-      <c r="BA10" s="16">
+      <c r="AR10" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS10" s="15">
+        <v>1</v>
+      </c>
+      <c r="AT10" s="15">
+        <v>0.36377326124460801</v>
+      </c>
+      <c r="AU10" s="15">
+        <v>2.8428392304449099E-3</v>
+      </c>
+      <c r="AV10" s="15">
+        <v>-1.2519185876994E-2</v>
+      </c>
+      <c r="AW10" s="15">
+        <v>1.6867429769903599E-3</v>
+      </c>
+      <c r="AX10" s="17">
+        <v>-1.09937236675108E-2</v>
+      </c>
+      <c r="AY10" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ10" s="15">
+        <v>1</v>
+      </c>
+      <c r="BA10" s="15">
         <v>0.378302585755525</v>
       </c>
-      <c r="BB10" s="16">
+      <c r="BB10" s="15">
         <v>1.5219142209891E-2</v>
       </c>
-      <c r="BC10" s="16">
+      <c r="BC10" s="15">
         <v>3.3402567090514798E-2</v>
       </c>
-      <c r="BD10" s="16">
+      <c r="BD10" s="15">
         <v>3.51298435276046E-2</v>
       </c>
-      <c r="BE10" s="18">
+      <c r="BE10" s="17">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="BF10" s="19">
+      <c r="BF10" s="18">
         <v>0.11314172811703556</v>
       </c>
-      <c r="BG10" s="16">
+      <c r="BG10" s="15">
         <v>0.115122399194304</v>
       </c>
-      <c r="BH10" s="16">
+      <c r="BH10" s="15">
         <v>0.114978230642938</v>
       </c>
-      <c r="BI10" s="16">
+      <c r="BI10" s="15">
         <v>0.111567130692639</v>
       </c>
-      <c r="BJ10" s="16">
+      <c r="BJ10" s="15">
         <v>0.10938133927183601</v>
       </c>
-      <c r="BK10" s="16">
+      <c r="BK10" s="15">
         <v>0.109663929299229</v>
       </c>
-      <c r="BL10" s="18">
+      <c r="BL10" s="17">
         <v>0.113</v>
       </c>
     </row>
@@ -2672,67 +2705,67 @@
       <c r="AQ11" s="12">
         <v>87</v>
       </c>
-      <c r="AR11" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS11" s="16">
-        <v>0.862222222222222</v>
-      </c>
-      <c r="AT11" s="16">
-        <v>0.58464646464646497</v>
-      </c>
-      <c r="AU11" s="16">
-        <v>0.55353535353535399</v>
-      </c>
-      <c r="AV11" s="16">
-        <v>0.55535353535353504</v>
-      </c>
-      <c r="AW11" s="16">
-        <v>0.530909090909091</v>
-      </c>
-      <c r="AX11" s="16">
-        <v>0.53818181818181798</v>
-      </c>
-      <c r="AY11" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ11" s="16">
+      <c r="AR11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS11" s="39">
+        <v>0.68962566974715001</v>
+      </c>
+      <c r="AT11" s="39">
+        <v>6.3462274292585996E-2</v>
+      </c>
+      <c r="AU11" s="39">
+        <v>-4.5231318091920698E-3</v>
+      </c>
+      <c r="AV11" s="39">
+        <v>1.4844227123438599E-2</v>
+      </c>
+      <c r="AW11" s="39">
+        <v>-8.9588672314802002E-3</v>
+      </c>
+      <c r="AX11" s="40">
+        <v>1.9349893898749099E-2</v>
+      </c>
+      <c r="AY11" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ11" s="15">
         <v>0.66806256481764403</v>
       </c>
-      <c r="BA11" s="16">
+      <c r="BA11" s="15">
         <v>8.5247056028629101E-2</v>
       </c>
-      <c r="BB11" s="16">
+      <c r="BB11" s="15">
         <v>1.37555907636112E-2</v>
       </c>
-      <c r="BC11" s="16">
+      <c r="BC11" s="15">
         <v>3.1206931386442399E-2</v>
       </c>
-      <c r="BD11" s="16">
+      <c r="BD11" s="15">
         <v>9.9277367269479996E-3</v>
       </c>
-      <c r="BE11" s="18">
+      <c r="BE11" s="17">
         <v>3.5770684508839003E-2</v>
       </c>
-      <c r="BF11" s="19">
+      <c r="BF11" s="18">
         <v>0.11511589010391808</v>
       </c>
-      <c r="BG11" s="16">
+      <c r="BG11" s="15">
         <v>9.9599999999999994E-2</v>
       </c>
-      <c r="BH11" s="16">
+      <c r="BH11" s="15">
         <v>9.0399999999999994E-2</v>
       </c>
-      <c r="BI11" s="16">
+      <c r="BI11" s="15">
         <v>8.3699999999999997E-2</v>
       </c>
-      <c r="BJ11" s="16">
+      <c r="BJ11" s="15">
         <v>8.1093956329524194E-2</v>
       </c>
-      <c r="BK11" s="16">
+      <c r="BK11" s="15">
         <v>5.6409076281559903E-2</v>
       </c>
-      <c r="BL11" s="18">
+      <c r="BL11" s="17">
         <v>2.41E-2</v>
       </c>
     </row>
@@ -2866,67 +2899,67 @@
       <c r="AQ12" s="12">
         <v>69</v>
       </c>
-      <c r="AR12" s="15">
-        <v>0.98747474747474795</v>
-      </c>
-      <c r="AS12" s="16">
-        <v>0.80363636363636404</v>
-      </c>
-      <c r="AT12" s="16">
-        <v>0.62484848484848499</v>
-      </c>
-      <c r="AU12" s="16">
-        <v>0.57252525252525299</v>
-      </c>
-      <c r="AV12" s="16">
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="AW12" s="16">
-        <v>0.53717171717171697</v>
-      </c>
-      <c r="AX12" s="16">
-        <v>0.52849999999999997</v>
-      </c>
-      <c r="AY12" s="17">
+      <c r="AR12" s="16">
+        <v>0.97175810360220805</v>
+      </c>
+      <c r="AS12" s="15">
+        <v>0.57173657197351702</v>
+      </c>
+      <c r="AT12" s="15">
+        <v>0.169319132946713</v>
+      </c>
+      <c r="AU12" s="15">
+        <v>4.2320155932244301E-2</v>
+      </c>
+      <c r="AV12" s="15">
+        <v>2.0250750231417199E-2</v>
+      </c>
+      <c r="AW12" s="15">
+        <v>-7.7653503498513604E-3</v>
+      </c>
+      <c r="AX12" s="17">
+        <v>-7.9596470653719494E-3</v>
+      </c>
+      <c r="AY12" s="16">
         <v>0.95926742202225901</v>
       </c>
-      <c r="AZ12" s="16">
+      <c r="AZ12" s="15">
         <v>0.64196646013635394</v>
       </c>
-      <c r="BA12" s="16">
+      <c r="BA12" s="15">
         <v>0.24512560815880599</v>
       </c>
-      <c r="BB12" s="16">
+      <c r="BB12" s="15">
         <v>8.1420324335986005E-2</v>
       </c>
-      <c r="BC12" s="16">
+      <c r="BC12" s="15">
         <v>3.1764088670502601E-2</v>
       </c>
-      <c r="BD12" s="16">
+      <c r="BD12" s="15">
         <v>7.4599298072037003E-3</v>
       </c>
-      <c r="BE12" s="18">
+      <c r="BE12" s="17">
         <v>4.3200000000000002E-2</v>
       </c>
-      <c r="BF12" s="19">
+      <c r="BF12" s="18">
         <v>7.7263002920948565E-2</v>
       </c>
-      <c r="BG12" s="16">
+      <c r="BG12" s="15">
         <v>7.8206591715434995E-2</v>
       </c>
-      <c r="BH12" s="16">
+      <c r="BH12" s="15">
         <v>6.2670959310071397E-2</v>
       </c>
-      <c r="BI12" s="16">
+      <c r="BI12" s="15">
         <v>5.1773253567909197E-2</v>
       </c>
-      <c r="BJ12" s="16">
+      <c r="BJ12" s="15">
         <v>4.3552125851925E-2</v>
       </c>
-      <c r="BK12" s="16">
+      <c r="BK12" s="15">
         <v>1.7768905579835199E-2</v>
       </c>
-      <c r="BL12" s="18">
+      <c r="BL12" s="17">
         <v>2.8E-3</v>
       </c>
     </row>
@@ -3060,67 +3093,67 @@
       <c r="AQ13" s="12">
         <v>42.5</v>
       </c>
-      <c r="AR13" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS13" s="16">
-        <v>1</v>
-      </c>
-      <c r="AT13" s="16">
-        <v>0.71353535353535402</v>
-      </c>
-      <c r="AU13" s="16">
-        <v>0.60727272727272696</v>
-      </c>
-      <c r="AV13" s="16">
-        <v>0.53292929292929303</v>
-      </c>
-      <c r="AW13" s="16">
-        <v>0.52</v>
-      </c>
-      <c r="AX13" s="16">
-        <v>0.54303030303030297</v>
-      </c>
-      <c r="AY13" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ13" s="16">
-        <v>1</v>
-      </c>
-      <c r="BA13" s="16">
+      <c r="AR13" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="15">
+        <v>0.356654158004368</v>
+      </c>
+      <c r="AU13" s="15">
+        <v>0.11256829714151199</v>
+      </c>
+      <c r="AV13" s="15">
+        <v>7.0453586719374604E-3</v>
+      </c>
+      <c r="AW13" s="15">
+        <v>-8.4452098852530206E-3</v>
+      </c>
+      <c r="AX13" s="17">
+        <v>-6.2217899063469403E-3</v>
+      </c>
+      <c r="AY13" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ13" s="15">
+        <v>1</v>
+      </c>
+      <c r="BA13" s="15">
         <v>0.36388134623454599</v>
       </c>
-      <c r="BB13" s="16">
+      <c r="BB13" s="15">
         <v>0.12946870134933</v>
       </c>
-      <c r="BC13" s="16">
+      <c r="BC13" s="15">
         <v>2.6516513928178002E-2</v>
       </c>
-      <c r="BD13" s="16">
+      <c r="BD13" s="15">
         <v>4.0528373826106898E-3</v>
       </c>
-      <c r="BE13" s="18">
+      <c r="BE13" s="17">
         <v>1.7355604338624899E-2</v>
       </c>
-      <c r="BF13" s="19">
+      <c r="BF13" s="18">
         <v>6.8686018315558525E-2</v>
       </c>
-      <c r="BG13" s="20">
+      <c r="BG13" s="19">
         <v>5.9680765230052599E-2</v>
       </c>
-      <c r="BH13" s="20">
+      <c r="BH13" s="19">
         <v>1.9673285143049501E-2</v>
       </c>
-      <c r="BI13" s="20">
+      <c r="BI13" s="19">
         <v>1.9673285143049501E-2</v>
       </c>
-      <c r="BJ13" s="20">
+      <c r="BJ13" s="19">
         <v>8.5638637254042606E-3</v>
       </c>
-      <c r="BK13" s="20">
+      <c r="BK13" s="19">
         <v>-4.8758792296344803E-3</v>
       </c>
-      <c r="BL13" s="18">
+      <c r="BL13" s="17">
         <v>1.7100000000000001E-2</v>
       </c>
     </row>
@@ -3254,261 +3287,261 @@
       <c r="AQ14" s="12">
         <v>20.5</v>
       </c>
-      <c r="AR14" s="15">
-        <v>1</v>
-      </c>
-      <c r="AS14" s="16">
-        <v>0.72606060606060596</v>
-      </c>
-      <c r="AT14" s="16">
-        <v>0.63818181818181796</v>
-      </c>
-      <c r="AU14" s="16">
-        <v>0.52202020202020205</v>
-      </c>
-      <c r="AV14" s="16">
-        <v>0.54141414141414201</v>
-      </c>
-      <c r="AW14" s="16">
-        <v>0.50303030303030305</v>
-      </c>
-      <c r="AX14" s="16">
-        <v>0.47030303030303</v>
-      </c>
-      <c r="AY14" s="17">
-        <v>1</v>
-      </c>
-      <c r="AZ14" s="16">
+      <c r="AR14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS14" s="15">
+        <v>0.42742826901675701</v>
+      </c>
+      <c r="AT14" s="15">
+        <v>0.223254092625468</v>
+      </c>
+      <c r="AU14" s="15">
+        <v>1.33389676895618E-2</v>
+      </c>
+      <c r="AV14" s="15">
+        <v>-1.5886212788132799E-2</v>
+      </c>
+      <c r="AW14" s="15">
+        <v>-7.6919575804469701E-3</v>
+      </c>
+      <c r="AX14" s="17">
+        <v>-1.08339744391538E-2</v>
+      </c>
+      <c r="AY14" s="16">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="15">
         <v>0.58847603064995302</v>
       </c>
-      <c r="BA14" s="16">
+      <c r="BA14" s="15">
         <v>0.27500298840570497</v>
       </c>
-      <c r="BB14" s="16">
+      <c r="BB14" s="15">
         <v>2.3474525322439301E-2</v>
       </c>
-      <c r="BC14" s="16">
+      <c r="BC14" s="15">
         <v>3.4726298900014702E-3</v>
       </c>
-      <c r="BD14" s="16">
+      <c r="BD14" s="15">
         <v>2.08998590154751E-2</v>
       </c>
-      <c r="BE14" s="18">
+      <c r="BE14" s="17">
         <v>5.8318662901035599E-3</v>
       </c>
-      <c r="BF14" s="19" t="s">
+      <c r="BF14" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="BG14" s="16">
+      <c r="BG14" s="15">
         <v>-6.4861915903689704E-3</v>
       </c>
-      <c r="BH14" s="16">
+      <c r="BH14" s="15">
         <v>1.5207326363231299E-3</v>
       </c>
-      <c r="BI14" s="16">
+      <c r="BI14" s="15">
         <v>-7.5201605746279803E-3</v>
       </c>
-      <c r="BJ14" s="16">
+      <c r="BJ14" s="15">
         <v>-7.3262913900794197E-3</v>
       </c>
-      <c r="BK14" s="16">
+      <c r="BK14" s="15">
         <v>-2.8178910805535399E-3</v>
       </c>
-      <c r="BL14" s="18">
+      <c r="BL14" s="17">
         <v>-2.2000000000000001E-3</v>
       </c>
     </row>
     <row r="15" spans="1:64" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" s="22">
-        <v>1</v>
-      </c>
-      <c r="C15" s="23">
+      <c r="A15" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="21">
+        <v>1</v>
+      </c>
+      <c r="C15" s="22">
         <v>0.78230963673961296</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <v>0.69990844958563303</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="22">
         <v>0.636956807104615</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="22">
         <v>0.59708873702092302</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <v>0.56798027377453597</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="23">
         <v>0.50103718151006504</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <v>56.8</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="25">
         <v>59.388489208633104</v>
       </c>
-      <c r="K15" s="26">
+      <c r="K15" s="25">
         <v>58.534990189666402</v>
       </c>
-      <c r="L15" s="26">
+      <c r="L15" s="25">
         <v>57.676258992805799</v>
       </c>
-      <c r="M15" s="26">
+      <c r="M15" s="25">
         <v>55.105006903568103</v>
       </c>
-      <c r="N15" s="26">
+      <c r="N15" s="25">
         <v>53.128406365816403</v>
       </c>
-      <c r="O15" s="27">
+      <c r="O15" s="26">
         <v>39.690647482014398</v>
       </c>
-      <c r="P15" s="28">
+      <c r="P15" s="27">
         <v>61.52</v>
       </c>
-      <c r="Q15" s="26">
+      <c r="Q15" s="25">
         <v>72.369565217391298</v>
       </c>
-      <c r="R15" s="26">
+      <c r="R15" s="25">
         <v>73.6714975845411</v>
       </c>
-      <c r="S15" s="26">
+      <c r="S15" s="25">
         <v>76.4673913043478</v>
       </c>
-      <c r="T15" s="26">
+      <c r="T15" s="25">
         <v>73.023715415019794</v>
       </c>
-      <c r="U15" s="26">
+      <c r="U15" s="25">
         <v>71.629336846728094</v>
       </c>
-      <c r="V15" s="26">
+      <c r="V15" s="25">
         <v>45.1086956521739</v>
       </c>
-      <c r="W15" s="25">
+      <c r="W15" s="24">
         <v>62.84</v>
       </c>
-      <c r="X15" s="26">
+      <c r="X15" s="25">
         <v>63.716981132075503</v>
       </c>
-      <c r="Y15" s="26">
+      <c r="Y15" s="25">
         <v>62.095006670478398</v>
       </c>
-      <c r="Z15" s="26">
+      <c r="Z15" s="25">
         <v>60.5589622641509</v>
       </c>
-      <c r="AA15" s="26">
+      <c r="AA15" s="25">
         <v>58.883647798742103</v>
       </c>
-      <c r="AB15" s="26">
+      <c r="AB15" s="25">
         <v>56.8491518963217</v>
       </c>
-      <c r="AC15" s="29">
+      <c r="AC15" s="28">
         <v>44.882075471698101</v>
       </c>
-      <c r="AD15" s="28">
+      <c r="AD15" s="27">
         <v>26.98</v>
       </c>
-      <c r="AE15" s="26">
+      <c r="AE15" s="25">
         <v>34.035714285714299</v>
       </c>
-      <c r="AF15" s="26">
+      <c r="AF15" s="25">
         <v>29.446428571428601</v>
       </c>
-      <c r="AG15" s="26">
+      <c r="AG15" s="25">
         <v>29.785714285714299</v>
       </c>
-      <c r="AH15" s="26">
+      <c r="AH15" s="25">
         <v>27.375</v>
       </c>
-      <c r="AI15" s="26">
+      <c r="AI15" s="25">
         <v>27.875</v>
       </c>
-      <c r="AJ15" s="26">
+      <c r="AJ15" s="25">
         <v>22.7321428571429</v>
       </c>
-      <c r="AK15" s="30">
+      <c r="AK15" s="29">
         <v>50</v>
       </c>
-      <c r="AL15" s="26">
+      <c r="AL15" s="25">
         <v>56.5</v>
       </c>
-      <c r="AM15" s="26">
+      <c r="AM15" s="25">
         <v>62.121212121212103</v>
       </c>
-      <c r="AN15" s="26">
+      <c r="AN15" s="25">
         <v>68</v>
       </c>
-      <c r="AO15" s="26">
+      <c r="AO15" s="25">
         <v>69.191919191919197</v>
       </c>
-      <c r="AP15" s="26">
+      <c r="AP15" s="25">
         <v>65.151515151515198</v>
       </c>
-      <c r="AQ15" s="29">
+      <c r="AQ15" s="28">
         <v>63</v>
       </c>
-      <c r="AR15" s="31">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="32">
-        <v>0.77252525252525295</v>
-      </c>
-      <c r="AT15" s="32">
-        <v>0.49616161616161603</v>
-      </c>
-      <c r="AU15" s="32">
-        <v>0.54626262626262601</v>
-      </c>
-      <c r="AV15" s="32">
-        <v>0.51272727272727303</v>
-      </c>
-      <c r="AW15" s="32">
-        <v>0.50060606060606105</v>
-      </c>
-      <c r="AX15" s="32">
-        <v>0.54787878787878797</v>
-      </c>
-      <c r="AY15" s="33">
-        <v>1</v>
-      </c>
-      <c r="AZ15" s="32">
+      <c r="AR15" s="16">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="39">
+        <v>0.48929093383056999</v>
+      </c>
+      <c r="AT15" s="39">
+        <v>1.6308994118629402E-2</v>
+      </c>
+      <c r="AU15" s="39">
+        <v>3.2020794265870102E-2</v>
+      </c>
+      <c r="AV15" s="39">
+        <v>1.2182680517823201E-2</v>
+      </c>
+      <c r="AW15" s="39">
+        <v>-1.50874617117687E-3</v>
+      </c>
+      <c r="AX15" s="40">
+        <v>-1.0732572866883601E-2</v>
+      </c>
+      <c r="AY15" s="31">
+        <v>1</v>
+      </c>
+      <c r="AZ15" s="30">
         <v>0.52555321594732696</v>
       </c>
-      <c r="BA15" s="32">
+      <c r="BA15" s="30">
         <v>1.9924386837663899E-2</v>
       </c>
-      <c r="BB15" s="32">
+      <c r="BB15" s="30">
         <v>6.2117999845442397E-2</v>
       </c>
-      <c r="BC15" s="32">
+      <c r="BC15" s="30">
         <v>3.56681605681387E-2</v>
       </c>
-      <c r="BD15" s="32">
+      <c r="BD15" s="30">
         <v>1.5825501198697502E-2</v>
       </c>
-      <c r="BE15" s="34">
+      <c r="BE15" s="32">
         <v>6.5105253733777598E-3</v>
       </c>
-      <c r="BF15" s="35">
+      <c r="BF15" s="33">
         <v>4.5448492022238163E-2</v>
       </c>
-      <c r="BG15" s="32">
+      <c r="BG15" s="30">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="BH15" s="32">
+      <c r="BH15" s="30">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="BI15" s="32">
+      <c r="BI15" s="30">
         <v>4.0300000000000002E-2</v>
       </c>
-      <c r="BJ15" s="32">
+      <c r="BJ15" s="30">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="BK15" s="32">
+      <c r="BK15" s="30">
         <v>5.0200000000000002E-2</v>
       </c>
-      <c r="BL15" s="34">
+      <c r="BL15" s="32">
         <v>2E-3</v>
       </c>
     </row>
